--- a/research/runs/20260228-180047-excel-compat-empirical-pass-01/fixtures/formula_parse_wave1/SCN-EB030-AMBIG-DOUBLE-COMMA.xlsx
+++ b/research/runs/20260228-180047-excel-compat-empirical-pass-01/fixtures/formula_parse_wave1/SCN-EB030-AMBIG-DOUBLE-COMMA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260228-180047-excel-compat-empirical-pass-01\fixtures\formula_parse_wave1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0820C170-DA5D-4C61-B87D-843DEC1D7F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12660738-C4F1-4B58-B9ED-05B844BA491E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7440" yWindow="3075" windowWidth="17460" windowHeight="11595" xr2:uid="{DC5ADAAC-B62D-43A6-B5D9-ED5FEA2AFAFE}"/>
   </bookViews>
